--- a/Design-Files/Pukk-Sensor-Module-v1.0/BOM/JLCPCB-BOM-Pukk-Sensor-Module-v1.0.xlsx
+++ b/Design-Files/Pukk-Sensor-Module-v1.0/BOM/JLCPCB-BOM-Pukk-Sensor-Module-v1.0.xlsx
@@ -756,13 +756,13 @@
     <t>C179739</t>
   </si>
   <si>
-    <t>2471841RL</t>
-  </si>
-  <si>
     <t>C1974498</t>
   </si>
   <si>
     <t>C137948</t>
+  </si>
+  <si>
+    <t>C3013790</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1578,7 @@
         <v>149</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1984,7 +1984,7 @@
         <v>160</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2264,7 +2264,7 @@
         <v>173</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
